--- a/Pruebas calificadas/COLEGIO-CIUDADELA-EL-RECREO-SONIA-OSORIO-DE-SAINT-MALO-(IED)-702_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CIUDADELA-EL-RECREO-SONIA-OSORIO-DE-SAINT-MALO-(IED)-702_CALIFICADO.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ72"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18621,6 +18621,1217 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>111001801098</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDADELA EL RECREO SONIA OSORIO DE SAINT-MALO (IED)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>EILEEN MARIAN ESTEVEZ FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>1145325781</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr"/>
+      <c r="X73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr"/>
+      <c r="AB73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI73" s="2" t="inlineStr"/>
+      <c r="AJ73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK73" s="2" t="inlineStr"/>
+      <c r="AL73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM73" s="2" t="inlineStr"/>
+      <c r="AN73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO73" s="2" t="inlineStr"/>
+      <c r="AP73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ73" s="2" t="inlineStr"/>
+      <c r="AR73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS73" s="2" t="inlineStr"/>
+      <c r="AT73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU73" s="2" t="inlineStr"/>
+      <c r="AV73" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW73" s="5">
+        <f>COUNTIF(J73:AV73,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX73" s="5">
+        <f>COUNTIF(J73:AV73,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY73" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ73" s="6">
+        <f>AW73/AY73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>111001801098</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDADELA EL RECREO SONIA OSORIO DE SAINT-MALO (IED)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>MICHAEL ALEJANDRO FERNANDEZ BERNAL</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1028872698</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG74" s="2" t="inlineStr"/>
+      <c r="AH74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK74" s="2" t="inlineStr"/>
+      <c r="AL74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM74" s="2" t="inlineStr"/>
+      <c r="AN74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO74" s="2" t="inlineStr"/>
+      <c r="AP74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ74" s="2" t="inlineStr"/>
+      <c r="AR74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS74" s="2" t="inlineStr"/>
+      <c r="AT74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU74" s="2" t="inlineStr"/>
+      <c r="AV74" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW74" s="5">
+        <f>COUNTIF(J74:AV74,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX74" s="5">
+        <f>COUNTIF(J74:AV74,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY74" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ74" s="6">
+        <f>AW74/AY74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>111001801098</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDADELA EL RECREO SONIA OSORIO DE SAINT-MALO (IED)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>TEDDY JESUS RODRIGUEZ BALZAN</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1016118452</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr"/>
+      <c r="X75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG75" s="2" t="inlineStr"/>
+      <c r="AH75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI75" s="2" t="inlineStr"/>
+      <c r="AJ75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK75" s="2" t="inlineStr"/>
+      <c r="AL75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM75" s="2" t="inlineStr"/>
+      <c r="AN75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO75" s="2" t="inlineStr"/>
+      <c r="AP75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ75" s="2" t="inlineStr"/>
+      <c r="AR75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS75" s="2" t="inlineStr"/>
+      <c r="AT75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU75" s="2" t="inlineStr"/>
+      <c r="AV75" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW75" s="5">
+        <f>COUNTIF(J75:AV75,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX75" s="5">
+        <f>COUNTIF(J75:AV75,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY75" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ75" s="6">
+        <f>AW75/AY75</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>111001801098</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDADELA EL RECREO SONIA OSORIO DE SAINT-MALO (IED)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>ANDRES MATIAS DONATO COCA</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1012427425</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr"/>
+      <c r="AB76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG76" s="2" t="inlineStr"/>
+      <c r="AH76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI76" s="2" t="inlineStr"/>
+      <c r="AJ76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK76" s="2" t="inlineStr"/>
+      <c r="AL76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM76" s="2" t="inlineStr"/>
+      <c r="AN76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO76" s="2" t="inlineStr"/>
+      <c r="AP76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ76" s="2" t="inlineStr"/>
+      <c r="AR76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS76" s="2" t="inlineStr"/>
+      <c r="AT76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU76" s="2" t="inlineStr"/>
+      <c r="AV76" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW76" s="5">
+        <f>COUNTIF(J76:AV76,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX76" s="5">
+        <f>COUNTIF(J76:AV76,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY76" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ76" s="6">
+        <f>AW76/AY76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>111001801098</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDADELA EL RECREO SONIA OSORIO DE SAINT-MALO (IED)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>JUAN DIEGO GUERRERO LEON</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>1012395005</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr"/>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG77" s="2" t="inlineStr"/>
+      <c r="AH77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI77" s="2" t="inlineStr"/>
+      <c r="AJ77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK77" s="2" t="inlineStr"/>
+      <c r="AL77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM77" s="2" t="inlineStr"/>
+      <c r="AN77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO77" s="2" t="inlineStr"/>
+      <c r="AP77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ77" s="2" t="inlineStr"/>
+      <c r="AR77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS77" s="2" t="inlineStr"/>
+      <c r="AT77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU77" s="2" t="inlineStr"/>
+      <c r="AV77" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW77" s="5">
+        <f>COUNTIF(J77:AV77,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX77" s="5">
+        <f>COUNTIF(J77:AV77,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY77" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ77" s="6">
+        <f>AW77/AY77</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>111001801098</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDADELA EL RECREO SONIA OSORIO DE SAINT-MALO (IED)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>SOL AINY CASTRO ARIAS</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1028894156</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr"/>
+      <c r="X78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG78" s="2" t="inlineStr"/>
+      <c r="AH78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI78" s="2" t="inlineStr"/>
+      <c r="AJ78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK78" s="2" t="inlineStr"/>
+      <c r="AL78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM78" s="2" t="inlineStr"/>
+      <c r="AN78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO78" s="2" t="inlineStr"/>
+      <c r="AP78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ78" s="2" t="inlineStr"/>
+      <c r="AR78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS78" s="2" t="inlineStr"/>
+      <c r="AT78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU78" s="2" t="inlineStr"/>
+      <c r="AV78" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW78" s="5">
+        <f>COUNTIF(J78:AV78,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX78" s="5">
+        <f>COUNTIF(J78:AV78,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY78" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ78" s="6">
+        <f>AW78/AY78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>111001801098</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO CIUDADELA EL RECREO SONIA OSORIO DE SAINT-MALO (IED)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>MARIA FERNANDA CHAVARRIO CASTILLO</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1023930837</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>702</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr"/>
+      <c r="X79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG79" s="2" t="inlineStr"/>
+      <c r="AH79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI79" s="2" t="inlineStr"/>
+      <c r="AJ79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK79" s="2" t="inlineStr"/>
+      <c r="AL79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM79" s="2" t="inlineStr"/>
+      <c r="AN79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO79" s="2" t="inlineStr"/>
+      <c r="AP79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ79" s="2" t="inlineStr"/>
+      <c r="AR79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS79" s="2" t="inlineStr"/>
+      <c r="AT79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU79" s="2" t="inlineStr"/>
+      <c r="AV79" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW79" s="5">
+        <f>COUNTIF(J79:AV79,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX79" s="5">
+        <f>COUNTIF(J79:AV79,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY79" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ79" s="6">
+        <f>AW79/AY79</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pruebas calificadas/COLEGIO-CIUDADELA-EL-RECREO-SONIA-OSORIO-DE-SAINT-MALO-(IED)-702_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CIUDADELA-EL-RECREO-SONIA-OSORIO-DE-SAINT-MALO-(IED)-702_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -1771,11 +1755,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2024,11 +2004,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2277,11 +2253,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2530,11 +2502,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -2783,11 +2751,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3036,11 +3000,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3289,11 +3249,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3542,11 +3498,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -3795,11 +3747,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4048,11 +3996,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4301,11 +4245,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4554,11 +4494,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -4807,11 +4743,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5060,11 +4992,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5313,11 +5241,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5566,11 +5490,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -5819,11 +5739,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6072,11 +5988,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6325,11 +6237,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6578,11 +6486,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -6831,11 +6735,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7080,11 +6980,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7333,11 +7229,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7582,11 +7474,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -7835,11 +7723,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8088,11 +7972,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8333,11 +8213,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8558,11 +8434,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -8811,11 +8683,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9064,11 +8932,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9317,11 +9181,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9570,11 +9430,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -9823,11 +9679,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10076,11 +9928,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10329,11 +10177,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10582,11 +10426,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -10831,11 +10671,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11084,11 +10920,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11333,11 +11165,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11586,11 +11414,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -11839,11 +11663,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12092,11 +11912,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12345,11 +12161,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12598,11 +12410,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -12851,11 +12659,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13104,11 +12908,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13357,11 +13157,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13610,11 +13406,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -13863,11 +13655,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14116,11 +13904,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14369,11 +14153,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14622,11 +14402,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -14875,11 +14651,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -15128,11 +14900,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -15381,11 +15149,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -15634,11 +15398,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -15887,11 +15647,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -16140,11 +15896,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -16393,11 +16145,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -16610,11 +16358,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -16863,11 +16607,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -17116,11 +16856,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -17365,11 +17101,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -17614,11 +17346,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -17863,11 +17591,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -18116,11 +17840,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -18369,11 +18089,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -18622,11 +18338,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -18795,11 +18507,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -18968,11 +18676,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -19141,11 +18845,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -19314,11 +19014,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -19487,11 +19183,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
@@ -19660,11 +19352,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001801098</t>
